--- a/graphy/감사조서/graphy_mapping_list_25년.xlsx
+++ b/graphy/감사조서/graphy_mapping_list_25년.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="129">
   <si>
     <t>계정명</t>
   </si>
@@ -401,6 +401,346 @@
     <t>move_image</t>
   </si>
   <si>
+    <t>graphy_벤포드_외상매출금_차변</t>
+  </si>
+  <si>
+    <t>벤포드 분석</t>
+  </si>
+  <si>
+    <t>벤포드 분석_외상매출금_차변</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>graphy_벤포드_외상매입금_대변</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>벤포드</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>분석</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>외상매입금</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>대변</t>
+    </r>
+  </si>
+  <si>
+    <t>국내상품매출액</t>
+  </si>
+  <si>
+    <t>graphy_벤포드_국내상품매출액_대변</t>
+  </si>
+  <si>
+    <t>벤포드 분석_국내상품매출액</t>
+  </si>
+  <si>
+    <t>graphy_벤포드_해외상품매출액_대변</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>벤포드</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>분석</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>해외</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>상품매출액</t>
+    </r>
+  </si>
+  <si>
+    <t>graphy_벤포드_국내제품매출액_대변</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>벤포드</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>분석</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>국내제</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>품매출액</t>
+    </r>
+  </si>
+  <si>
+    <t>graphy_벤포드_해외제품매출액_대변</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>벤포드</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>분석</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>해외제</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>품매출액</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>graphy_상대계정분석</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>외상매출금_차변</t>
+    </r>
+  </si>
+  <si>
+    <t>상대계정목록</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>상대계정분석_외상매출금</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>차변</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t>graphy_</t>
     </r>
@@ -412,6 +752,594 @@
         <sz val="10"/>
         <rFont val="맑은 고딕"/>
       </rPr>
+      <t>상대계정분석</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>외상매입금_대변</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>상대계정분석_외상매입금</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>대</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>변</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>graphy_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>상대계정분석</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>해외제품매출액</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>_대변</t>
+    </r>
+  </si>
+  <si>
+    <t>상대계정분석_해외제품매출액</t>
+  </si>
+  <si>
+    <r>
+      <t>graphy_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>상대계정분석</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>국내제품매출액</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>_대변</t>
+    </r>
+  </si>
+  <si>
+    <t>상대계정분석_국내제품매출액</t>
+  </si>
+  <si>
+    <r>
+      <t>graphy_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>상대계정분석</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>해외상품매출애</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>_대변</t>
+    </r>
+  </si>
+  <si>
+    <t>상대계정분석_해외상품매출애</t>
+  </si>
+  <si>
+    <r>
+      <t>graphy_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>상대계정분석</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>국내상품매출액</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>_대변</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>상대계정분석</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>국내상품매출액</t>
+    </r>
+  </si>
+  <si>
+    <t>graphy_전기비교_해외제품매출액</t>
+  </si>
+  <si>
+    <t>전기비교</t>
+  </si>
+  <si>
+    <t>전기당기비교_해외제품매출액</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <r>
+      <t>graphy_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>전기비교</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>국내</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>제품매출액</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>전기당기비교</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>국내</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>제품매출액</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>graphy_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>전기비교</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>해외상품</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>매출액</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>전기당기비교</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>해외상품</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>매출액</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>graphy_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>전기비교</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>국내상품</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>매출액</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>전기당기비교</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>국내상품</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>매출액</t>
+    </r>
+  </si>
+  <si>
+    <t>일반사항분석</t>
+  </si>
+  <si>
+    <t>graphy_일반사항분석</t>
+  </si>
+  <si>
+    <t>계정별상세내역</t>
+  </si>
+  <si>
+    <t>analysis_inject</t>
+  </si>
+  <si>
+    <t>사용권자산_리스부채</t>
+  </si>
+  <si>
+    <t>lease_schedule_graphy</t>
+  </si>
+  <si>
+    <t>계약별 요약</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>LEASE_INJECT</t>
+  </si>
+  <si>
+    <t>보통예금</t>
+  </si>
+  <si>
+    <r>
+      <t>graphy_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
       <t>벤포드</t>
     </r>
     <r>
@@ -427,30 +1355,103 @@
       <rPr>
         <charset val="129"/>
         <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>외상매출금</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>_차변</t>
-    </r>
-  </si>
-  <si>
-    <t>벤포드 분석</t>
-  </si>
-  <si>
-    <t>벤포드 분석_외상매출금_차변</t>
-  </si>
-  <si>
-    <t>A5</t>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>보통예금</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>차변</t>
+    </r>
+  </si>
+  <si>
+    <t>JET_25년</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>벤포드</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>분석</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>보통예금</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>차변</t>
+    </r>
   </si>
   <si>
     <r>
@@ -479,20 +1480,30 @@
       <rPr>
         <charset val="129"/>
         <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>외상매입금</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>_대변</t>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>보통예금</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>대변</t>
     </r>
   </si>
   <si>
@@ -538,11 +1549,11 @@
       <rPr>
         <charset val="129"/>
         <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>외상매입금</t>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>보통예금</t>
     </r>
     <r>
       <rPr>
@@ -561,16 +1572,86 @@
         <sz val="10"/>
         <rFont val="맑은 고딕"/>
       </rPr>
+      <t>대</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>변</t>
+    </r>
+  </si>
+  <si>
+    <t>미지급금</t>
+  </si>
+  <si>
+    <r>
+      <t>graphy_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>벤포드</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>미지급</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>금</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
       <t>대변</t>
     </r>
   </si>
   <si>
-    <t>국내상품매출액</t>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
     <r>
       <rPr>
         <charset val="129"/>
@@ -588,6 +1669,25 @@
         <sz val="10"/>
         <rFont val="Arial"/>
       </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>분석</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF444746"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
       <t>_</t>
     </r>
     <r>
@@ -598,7 +1698,17 @@
         <sz val="10"/>
         <rFont val="맑은 고딕"/>
       </rPr>
-      <t>국내상품매출액</t>
+      <t>미지급</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="129"/>
+        <color rgb="FF444746"/>
+        <family val="3"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>금</t>
     </r>
     <r>
       <rPr>
@@ -619,1414 +1729,6 @@
       </rPr>
       <t>대변</t>
     </r>
-  </si>
-  <si>
-    <t>벤포드 분석_국내상품매출액</t>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>해외상품매출액</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>대변</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>분석</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>해외</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>상품매출액</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>국내제품매출액</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>대변</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>분석</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>국내제</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>품매출액</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>해외제품매출액</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>대변</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>분석</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>해외제</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>품매출액</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>graphy_상대계정분석</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>외상매출금_차변</t>
-    </r>
-  </si>
-  <si>
-    <t>상대계정목록</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>상대계정분석_외상매출금</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>차변</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>상대계정분석</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>외상매입금_대변</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>상대계정분석_외상매입금</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>대</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>변</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>상대계정분석</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>해외제품매출액</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>_대변</t>
-    </r>
-  </si>
-  <si>
-    <t>상대계정분석_해외제품매출액</t>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>상대계정분석</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>국내제품매출액</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>_대변</t>
-    </r>
-  </si>
-  <si>
-    <t>상대계정분석_국내제품매출액</t>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>상대계정분석</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>해외상품매출애</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>_대변</t>
-    </r>
-  </si>
-  <si>
-    <t>상대계정분석_해외상품매출애</t>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>상대계정분석</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>국내상품매출액</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>_대변</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>상대계정분석</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>국내상품매출액</t>
-    </r>
-  </si>
-  <si>
-    <t>graphy_전기비교_해외제품매출액</t>
-  </si>
-  <si>
-    <t>전기비교</t>
-  </si>
-  <si>
-    <t>전기당기비교_해외제품매출액</t>
-  </si>
-  <si>
-    <t>A9</t>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>전기비교</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>국내</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>제품매출액</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>전기당기비교</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>국내</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>제품매출액</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>전기비교</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>해외상품</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>매출액</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>전기당기비교</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>해외상품</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>매출액</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>전기비교</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>국내상품</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>매출액</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>전기당기비교</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>국내상품</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>매출액</t>
-    </r>
-  </si>
-  <si>
-    <t>일반사항분석</t>
-  </si>
-  <si>
-    <t>graphy_일반사항분석</t>
-  </si>
-  <si>
-    <t>계정별상세내역</t>
-  </si>
-  <si>
-    <t>analysis_inject</t>
-  </si>
-  <si>
-    <t>사용권자산_리스부채</t>
-  </si>
-  <si>
-    <t>lease_schedule_graphy</t>
-  </si>
-  <si>
-    <t>계약별 요약</t>
-  </si>
-  <si>
-    <t>B6</t>
-  </si>
-  <si>
-    <t>LEASE_INJECT</t>
-  </si>
-  <si>
-    <t>보통예금</t>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>보통예금</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>차변</t>
-    </r>
-  </si>
-  <si>
-    <t>JET_25년</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>분석</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>보통예금</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>차변</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>보통예금</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>대변</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>분석</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>보통예금</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>대</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>변</t>
-    </r>
-  </si>
-  <si>
-    <t>graphy_벤포드_외상매출금_차변</t>
-  </si>
-  <si>
-    <t>graphy_벤포드_외상매입금_대변</t>
-  </si>
-  <si>
-    <t>미지급금</t>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>미지급</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>금</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>대변</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>분석</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>미지급</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="3"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>금</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color rgb="FF444746"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>대변</t>
-    </r>
-  </si>
-  <si>
-    <t>graphy_벤포드_국내상품매출액_대변</t>
-  </si>
-  <si>
-    <t>graphy_벤포드_해외상품매출액_대변</t>
-  </si>
-  <si>
-    <t>graphy_벤포드_국내제품매출액_대변</t>
-  </si>
-  <si>
-    <t>graphy_벤포드_해외제품매출액_대변</t>
   </si>
   <si>
     <t>공휴일전표</t>
@@ -3419,7 +3121,7 @@
         <v>9</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>56</v>
@@ -3442,7 +3144,7 @@
         <v>22</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>56</v>
@@ -3462,10 +3164,10 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>56</v>
@@ -3475,7 +3177,7 @@
         <v>104</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>58</v>
@@ -3488,7 +3190,7 @@
         <v>61</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>56</v>
@@ -3511,7 +3213,7 @@
         <v>26</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>56</v>
@@ -3534,7 +3236,7 @@
         <v>30</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>56</v>
@@ -3557,7 +3259,7 @@
         <v>33</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>56</v>
@@ -3715,20 +3417,20 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="14" t="s">
         <v>104</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>20</v>
@@ -3747,26 +3449,26 @@
         <v>95</v>
       </c>
       <c r="D48" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>104</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H48" s="16"/>
       <c r="I48" s="15"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>56</v>
@@ -3779,7 +3481,7 @@
         <v>57</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="10" t="s">
@@ -3788,10 +3490,10 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>56</v>
@@ -3801,10 +3503,10 @@
         <v>13</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H50" s="7"/>
       <c r="I50" s="10" t="s">
@@ -3813,10 +3515,10 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>56</v>
@@ -3829,7 +3531,7 @@
         <v>63</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="10" t="s">
@@ -3838,10 +3540,10 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>56</v>
@@ -3851,10 +3553,10 @@
         <v>13</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H52" s="7"/>
       <c r="I52" s="10" t="s">
@@ -3863,10 +3565,10 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>56</v>
@@ -3876,10 +3578,10 @@
         <v>13</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="10" t="s">
@@ -3888,10 +3590,10 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>56</v>
@@ -3901,10 +3603,10 @@
         <v>13</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="10" t="s">

--- a/graphy/감사조서/graphy_mapping_list_25년.xlsx
+++ b/graphy/감사조서/graphy_mapping_list_25년.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220"/>
+    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="138">
   <si>
     <t>계정명</t>
   </si>
@@ -1767,7 +1767,7 @@
     <t>외상매출금_그래프</t>
   </si>
   <si>
-    <t>A23</t>
+    <t>A19</t>
   </si>
   <si>
     <t>외상매입금_그래프</t>
@@ -1795,6 +1795,33 @@
   </si>
   <si>
     <t>벤포드 분석_해외제품매출액</t>
+  </si>
+  <si>
+    <t>보통예금_차변_그래프</t>
+  </si>
+  <si>
+    <t>graphy_벤포드_보통예금_차변</t>
+  </si>
+  <si>
+    <t>벤포드 분석_보통예금_차변</t>
+  </si>
+  <si>
+    <t>보통예금_대변_그래프</t>
+  </si>
+  <si>
+    <t>graphy_벤포드_보통예금_대변</t>
+  </si>
+  <si>
+    <t>벤포드 분석_보통예금_대변</t>
+  </si>
+  <si>
+    <t>미지급금_그래프</t>
+  </si>
+  <si>
+    <t>graphy_벤포드_미지급금_대변</t>
+  </si>
+  <si>
+    <t>벤포드 분석_미지급금_대변</t>
   </si>
 </sst>
 </file>
@@ -1901,7 +1928,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1924,11 +1951,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1967,7 +2020,10 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2310,10 +2366,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr defaultRowHeight="17" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.08203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="38.08203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="26.1640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.9140625" style="1" customWidth="1"/>
@@ -2323,7 +2379,7 @@
     <col min="9" max="9" width="14.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2352,7 +2408,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -2377,7 +2433,7 @@
       <c r="H2" s="7"/>
       <c r="I2" s="10"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
@@ -2402,7 +2458,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
@@ -2427,7 +2483,7 @@
       <c r="H4" s="7"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>26</v>
       </c>
@@ -2452,7 +2508,7 @@
       <c r="H5" s="7"/>
       <c r="I5" s="10"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>30</v>
       </c>
@@ -2477,7 +2533,7 @@
       <c r="H6" s="7"/>
       <c r="I6" s="10"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>33</v>
       </c>
@@ -2502,7 +2558,7 @@
       <c r="H7" s="7"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>36</v>
       </c>
@@ -2527,7 +2583,7 @@
       <c r="H8" s="7"/>
       <c r="I8" s="10"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>39</v>
       </c>
@@ -2552,7 +2608,7 @@
       <c r="H9" s="7"/>
       <c r="I9" s="10"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>42</v>
       </c>
@@ -2577,7 +2633,7 @@
       <c r="H10" s="7"/>
       <c r="I10" s="10"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>45</v>
       </c>
@@ -2602,7 +2658,7 @@
       <c r="H11" s="7"/>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>48</v>
       </c>
@@ -2627,7 +2683,7 @@
       <c r="H12" s="7"/>
       <c r="I12" s="10"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>9</v>
       </c>
@@ -2652,7 +2708,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>9</v>
       </c>
@@ -2675,7 +2731,7 @@
       <c r="H14" s="7"/>
       <c r="I14" s="10"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
@@ -2698,7 +2754,7 @@
       <c r="H15" s="7"/>
       <c r="I15" s="10"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>61</v>
       </c>
@@ -2721,7 +2777,7 @@
       <c r="H16" s="7"/>
       <c r="I16" s="10"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>26</v>
       </c>
@@ -2744,7 +2800,7 @@
       <c r="H17" s="7"/>
       <c r="I17" s="10"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>30</v>
       </c>
@@ -2767,7 +2823,7 @@
       <c r="H18" s="7"/>
       <c r="I18" s="10"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>33</v>
       </c>
@@ -2790,7 +2846,7 @@
       <c r="H19" s="7"/>
       <c r="I19" s="10"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>9</v>
       </c>
@@ -2813,7 +2869,7 @@
       <c r="H20" s="7"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>22</v>
       </c>
@@ -2836,7 +2892,7 @@
       <c r="H21" s="7"/>
       <c r="I21" s="10"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>33</v>
       </c>
@@ -3425,14 +3481,14 @@
       <c r="C47" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D47" s="7"/>
-      <c r="E47" s="14" t="s">
+      <c r="D47" s="14"/>
+      <c r="E47" s="8" t="s">
         <v>104</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="G47" s="7" t="s">
+      <c r="G47" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H47" s="7"/>
@@ -3451,17 +3507,17 @@
       <c r="D48" t="s">
         <v>115</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="F48" s="15" t="s">
+      <c r="F48" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="G48" s="15" t="s">
+      <c r="G48" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="H48" s="16"/>
-      <c r="I48" s="15"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="16"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
@@ -3610,6 +3666,231 @@
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="7"/>
+      <c r="E58" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H58" s="7"/>
+      <c r="I58" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D59" s="7"/>
+      <c r="E59" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H59" s="7"/>
+      <c r="I59" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D60" s="7"/>
+      <c r="E60" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H60" s="7"/>
+      <c r="I60" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D61" s="7"/>
+      <c r="E61" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H61" s="7"/>
+      <c r="I61" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="7"/>
+      <c r="E62" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H62" s="7"/>
+      <c r="I62" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D63" s="7"/>
+      <c r="E63" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H63" s="7"/>
+      <c r="I63" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D64" s="7"/>
+      <c r="E64" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H64" s="7"/>
+      <c r="I64" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D65" s="7"/>
+      <c r="E65" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H65" s="7"/>
+      <c r="I65" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" s="7"/>
+      <c r="E66" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H66" s="7"/>
+      <c r="I66" s="10" t="s">
         <v>54</v>
       </c>
     </row>
